--- a/evergreen-training-data-v2/clients/EVG1003_Okafor/2025/EVG1003_2025_Software_Exception_Workbook.xlsx
+++ b/evergreen-training-data-v2/clients/EVG1003_Okafor/2025/EVG1003_2025_Software_Exception_Workbook.xlsx
@@ -10729,7 +10729,7 @@
       </c>
       <c r="G16" s="57" t="inlineStr">
         <is>
-          <t>Schedule 1-A qualified tips inputs (W-2 and Schedule C activity - verify field paths in current release): W-2 social-security tips $24,600 + Form 4137 tips $1,600 + rideshare rider tips $2,860 (limited to Schedule C net $16,647 - not limiting) = $29,060; deduction capped at $25,000. Occupation: bartender / rideshare driver (both on Treasury's list). MAGI $61,471 &lt; $150,000.</t>
+          <t>Schedule 1-A qualified tips inputs (W-2 and Schedule C activity - verify field paths in current release): W-2 social-security tips $24,600 + Form 4137 tips $1,600 + rideshare rider tips $2,860 (limited to Schedule C net $16,911 - not limiting) = $29,060; deduction capped at $25,000. Occupation: bartender / rideshare driver (both on Treasury's list). MAGI $61,716 &lt; $150,000.</t>
         </is>
       </c>
       <c r="H16" s="3" t="n">
